--- a/99 - Excels/Open-OMs.xlsx
+++ b/99 - Excels/Open-OMs.xlsx
@@ -1,34 +1,613 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3746A762-7257-4CAF-A23C-947000E5972E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="190">
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>685601472256</t>
+  </si>
+  <si>
+    <t>5212939</t>
+  </si>
+  <si>
+    <t>5212938</t>
+  </si>
+  <si>
+    <t>685601459272</t>
+  </si>
+  <si>
+    <t>5213517</t>
+  </si>
+  <si>
+    <t>5211998</t>
+  </si>
+  <si>
+    <t>685601482423</t>
+  </si>
+  <si>
+    <t>685601478874</t>
+  </si>
+  <si>
+    <t>685601448444</t>
+  </si>
+  <si>
+    <t>685601479812</t>
+  </si>
+  <si>
+    <t>685601477816</t>
+  </si>
+  <si>
+    <t>685601481316</t>
+  </si>
+  <si>
+    <t>5212576</t>
+  </si>
+  <si>
+    <t>5213577</t>
+  </si>
+  <si>
+    <t>5212520</t>
+  </si>
+  <si>
+    <t>5213607</t>
+  </si>
+  <si>
+    <t>5213566</t>
+  </si>
+  <si>
+    <t>5213286</t>
+  </si>
+  <si>
+    <t>5212967</t>
+  </si>
+  <si>
+    <t>685601476166</t>
+  </si>
+  <si>
+    <t>5213806</t>
+  </si>
+  <si>
+    <t>5212740</t>
+  </si>
+  <si>
+    <t>5212913</t>
+  </si>
+  <si>
+    <t>5212977</t>
+  </si>
+  <si>
+    <t>5213322</t>
+  </si>
+  <si>
+    <t>685601481991</t>
+  </si>
+  <si>
+    <t>5212762</t>
+  </si>
+  <si>
+    <t>685601476940</t>
+  </si>
+  <si>
+    <t>685601481241</t>
+  </si>
+  <si>
+    <t>685601484141</t>
+  </si>
+  <si>
+    <t>5213084</t>
+  </si>
+  <si>
+    <t>5213740</t>
+  </si>
+  <si>
+    <t>5209234</t>
+  </si>
+  <si>
+    <t>5209122</t>
+  </si>
+  <si>
+    <t>5209935</t>
+  </si>
+  <si>
+    <t>5210315</t>
+  </si>
+  <si>
+    <t>5209687</t>
+  </si>
+  <si>
+    <t>685601473792</t>
+  </si>
+  <si>
+    <t>685601473789</t>
+  </si>
+  <si>
+    <t>685601470339</t>
+  </si>
+  <si>
+    <t>685601473790</t>
+  </si>
+  <si>
+    <t>685601477710</t>
+  </si>
+  <si>
+    <t>685601477709</t>
+  </si>
+  <si>
+    <t>685601477295</t>
+  </si>
+  <si>
+    <t>685601477143</t>
+  </si>
+  <si>
+    <t>685601472058</t>
+  </si>
+  <si>
+    <t>685601475997</t>
+  </si>
+  <si>
+    <t>5210702</t>
+  </si>
+  <si>
+    <t>5211406</t>
+  </si>
+  <si>
+    <t>5211433</t>
+  </si>
+  <si>
+    <t>5211635</t>
+  </si>
+  <si>
+    <t>5210304</t>
+  </si>
+  <si>
+    <t>685601451494</t>
+  </si>
+  <si>
+    <t>685601472253</t>
+  </si>
+  <si>
+    <t>685601470912</t>
+  </si>
+  <si>
+    <t>685601473750</t>
+  </si>
+  <si>
+    <t>685601473748</t>
+  </si>
+  <si>
+    <t>685601473749</t>
+  </si>
+  <si>
+    <t>685601473752</t>
+  </si>
+  <si>
+    <t>685601472625</t>
+  </si>
+  <si>
+    <t>685601469648</t>
+  </si>
+  <si>
+    <t>685601474571</t>
+  </si>
+  <si>
+    <t>685601451993</t>
+  </si>
+  <si>
+    <t>685601473793</t>
+  </si>
+  <si>
+    <t>685601474427</t>
+  </si>
+  <si>
+    <t>685601475350</t>
+  </si>
+  <si>
+    <t>685601468863</t>
+  </si>
+  <si>
+    <t>5211980</t>
+  </si>
+  <si>
+    <t>5210056</t>
+  </si>
+  <si>
+    <t>5210496</t>
+  </si>
+  <si>
+    <t>5212006</t>
+  </si>
+  <si>
+    <t>5210150</t>
+  </si>
+  <si>
+    <t>5209082</t>
+  </si>
+  <si>
+    <t>5211156</t>
+  </si>
+  <si>
+    <t>685601475785</t>
+  </si>
+  <si>
+    <t>685601470936</t>
+  </si>
+  <si>
+    <t>685601476179</t>
+  </si>
+  <si>
+    <t>685601453036</t>
+  </si>
+  <si>
+    <t>685601473718</t>
+  </si>
+  <si>
+    <t>685601411643</t>
+  </si>
+  <si>
+    <t>685601471073</t>
+  </si>
+  <si>
+    <t>685601471068</t>
+  </si>
+  <si>
+    <t>685601454495</t>
+  </si>
+  <si>
+    <t>685601471071</t>
+  </si>
+  <si>
+    <t>685601478555</t>
+  </si>
+  <si>
+    <t>685601479591</t>
+  </si>
+  <si>
+    <t>685601479822</t>
+  </si>
+  <si>
+    <t>685601477480</t>
+  </si>
+  <si>
+    <t>685601470243</t>
+  </si>
+  <si>
+    <t>685601473677</t>
+  </si>
+  <si>
+    <t>685601476973</t>
+  </si>
+  <si>
+    <t>685601476965</t>
+  </si>
+  <si>
+    <t>685601470955</t>
+  </si>
+  <si>
+    <t>685601469659</t>
+  </si>
+  <si>
+    <t>685601476223</t>
+  </si>
+  <si>
+    <t>685601470356</t>
+  </si>
+  <si>
+    <t>685601452845</t>
+  </si>
+  <si>
+    <t>685601451795</t>
+  </si>
+  <si>
+    <t>685601425168</t>
+  </si>
+  <si>
+    <t>5208962</t>
+  </si>
+  <si>
+    <t>5205524</t>
+  </si>
+  <si>
+    <t>5212399</t>
+  </si>
+  <si>
+    <t>5212335</t>
+  </si>
+  <si>
+    <t>5212288</t>
+  </si>
+  <si>
+    <t>5212278</t>
+  </si>
+  <si>
+    <t>5212236</t>
+  </si>
+  <si>
+    <t>5212234</t>
+  </si>
+  <si>
+    <t>5211852</t>
+  </si>
+  <si>
+    <t>5211552</t>
+  </si>
+  <si>
+    <t>5211549</t>
+  </si>
+  <si>
+    <t>5211474</t>
+  </si>
+  <si>
+    <t>5211279</t>
+  </si>
+  <si>
+    <t>5211262</t>
+  </si>
+  <si>
+    <t>5211104</t>
+  </si>
+  <si>
+    <t>5211010</t>
+  </si>
+  <si>
+    <t>5212949</t>
+  </si>
+  <si>
+    <t>5212718</t>
+  </si>
+  <si>
+    <t>5212703</t>
+  </si>
+  <si>
+    <t>5212623</t>
+  </si>
+  <si>
+    <t>5212604</t>
+  </si>
+  <si>
+    <t>5212559</t>
+  </si>
+  <si>
+    <t>5212439</t>
+  </si>
+  <si>
+    <t>5212420</t>
+  </si>
+  <si>
+    <t>5212344</t>
+  </si>
+  <si>
+    <t>5212272</t>
+  </si>
+  <si>
+    <t>5212262</t>
+  </si>
+  <si>
+    <t>5212201</t>
+  </si>
+  <si>
+    <t>5211995</t>
+  </si>
+  <si>
+    <t>5211811</t>
+  </si>
+  <si>
+    <t>5211168</t>
+  </si>
+  <si>
+    <t>5210905</t>
+  </si>
+  <si>
+    <t>685601481941</t>
+  </si>
+  <si>
+    <t>685601481400</t>
+  </si>
+  <si>
+    <t>685601480215</t>
+  </si>
+  <si>
+    <t>685601480212</t>
+  </si>
+  <si>
+    <t>685601478557</t>
+  </si>
+  <si>
+    <t>685601478054</t>
+  </si>
+  <si>
+    <t>685601477826</t>
+  </si>
+  <si>
+    <t>685601477814</t>
+  </si>
+  <si>
+    <t>685601477812</t>
+  </si>
+  <si>
+    <t>685601477809</t>
+  </si>
+  <si>
+    <t>685601477779</t>
+  </si>
+  <si>
+    <t>685601477777</t>
+  </si>
+  <si>
+    <t>685601476967</t>
+  </si>
+  <si>
+    <t>685601476303</t>
+  </si>
+  <si>
+    <t>685601473709</t>
+  </si>
+  <si>
+    <t>685601472257</t>
+  </si>
+  <si>
+    <t>685601474034</t>
+  </si>
+  <si>
+    <t>685601469761</t>
+  </si>
+  <si>
+    <t>685601459228</t>
+  </si>
+  <si>
+    <t>685601456550</t>
+  </si>
+  <si>
+    <t>685601454184</t>
+  </si>
+  <si>
+    <t>685601392573</t>
+  </si>
+  <si>
+    <t>5212341</t>
+  </si>
+  <si>
+    <t>5212167</t>
+  </si>
+  <si>
+    <t>5212871</t>
+  </si>
+  <si>
+    <t>5212438</t>
+  </si>
+  <si>
+    <t>685601479811</t>
+  </si>
+  <si>
+    <t>685601480243</t>
+  </si>
+  <si>
+    <t>685601478071</t>
+  </si>
+  <si>
+    <t>685601480769</t>
+  </si>
+  <si>
+    <t>685601480247</t>
+  </si>
+  <si>
+    <t>685601478412</t>
+  </si>
+  <si>
+    <t>685601478200</t>
+  </si>
+  <si>
+    <t>685601478073</t>
+  </si>
+  <si>
+    <t>685601469536</t>
+  </si>
+  <si>
+    <t>5211571</t>
+  </si>
+  <si>
+    <t>5211931</t>
+  </si>
+  <si>
+    <t>5211718</t>
+  </si>
+  <si>
+    <t>5213332</t>
+  </si>
+  <si>
+    <t>5212759</t>
+  </si>
+  <si>
+    <t>5212863</t>
+  </si>
+  <si>
+    <t>5213045</t>
+  </si>
+  <si>
+    <t>5212370</t>
+  </si>
+  <si>
+    <t>5210615</t>
+  </si>
+  <si>
+    <t>5210625</t>
+  </si>
+  <si>
+    <t>685601476975</t>
+  </si>
+  <si>
+    <t>685601481198</t>
+  </si>
+  <si>
+    <t>685601476035</t>
+  </si>
+  <si>
+    <t>685601480975</t>
+  </si>
+  <si>
+    <t>685601444115</t>
+  </si>
+  <si>
+    <t>685601473578</t>
+  </si>
+  <si>
+    <t>685601477810</t>
+  </si>
+  <si>
+    <t>685601478879</t>
+  </si>
+  <si>
+    <t>685601450878</t>
+  </si>
+  <si>
+    <t>685601471729</t>
+  </si>
+  <si>
+    <t>685601444057</t>
+  </si>
+  <si>
+    <t>685601479642</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +625,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,129 +931,1006 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B198"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>OM</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>5211980</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>5210056</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5210496</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5212006</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5210150</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5209082</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5211156</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>5211980</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>685601475785</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>685601470936</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>685601476179</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>685601453036</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>685601473718</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>685601362032</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>685601473577</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>685601479539</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
